--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -3455,7 +3455,7 @@
         <v>46023</v>
       </c>
       <c r="C138" s="6" t="n">
-        <v>24.973976071</v>
+        <v>24.963384137</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>0.788493942</v>
@@ -3476,7 +3476,9 @@
       <c r="B139" s="5" t="n">
         <v>46113</v>
       </c>
-      <c r="C139" s="4" t="n"/>
+      <c r="C139" s="7" t="n">
+        <v>26.144132442</v>
+      </c>
       <c r="D139" s="7" t="n">
         <v>0.898248914</v>
       </c>
